--- a/AI-103/AI-103_6-Week_Study_Schedule_Updated_Balanced.xlsx
+++ b/AI-103/AI-103_6-Week_Study_Schedule_Updated_Balanced.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Ai Projects\docs\AI-103\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{731820A9-73CD-48BD-93EE-17B6A572C45F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2AD247E-F9CA-4ABE-B950-67154ADB1902}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Sheet1!$A$1:$R$44</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet2!$C$1:$J$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sheet2 (2)'!$C$1:$J$53</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Sheet5!$G$2:$L$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Sheet5!$G$2:$M$72</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1987" uniqueCount="586">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1997" uniqueCount="588">
   <si>
     <t>AI-103 6-Week Study Schedule — Updated Balanced Plan</t>
   </si>
@@ -1805,6 +1805,12 @@
   </si>
   <si>
     <t>42m</t>
+  </si>
+  <si>
+    <t>C5, C6</t>
+  </si>
+  <si>
+    <t>L2, L3, L4, L5</t>
   </si>
 </sst>
 </file>
@@ -1938,7 +1944,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -2027,6 +2033,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -12427,9 +12436,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2AB7417-8CF2-44FA-AA3F-F566B8BA0641}">
-  <dimension ref="G1:M84"/>
+  <dimension ref="B1:M84"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
+    <col min="4" max="4" width="11.875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="4.125" style="16" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.125" style="16" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7" style="16" bestFit="1" customWidth="1"/>
@@ -12439,7 +12449,7 @@
     <col min="13" max="13" width="9" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="7:13">
+    <row r="1" spans="2:13">
       <c r="G1" s="16" t="s">
         <v>532</v>
       </c>
@@ -12456,7 +12466,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="2" spans="7:13">
+    <row r="2" spans="2:13">
       <c r="G2" s="18">
         <v>1</v>
       </c>
@@ -12479,7 +12489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="7:13">
+    <row r="3" spans="2:13">
       <c r="G3" s="26">
         <v>2</v>
       </c>
@@ -12502,7 +12512,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="7:13">
+    <row r="4" spans="2:13">
       <c r="G4" s="26">
         <v>3</v>
       </c>
@@ -12525,7 +12535,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="7:13">
+    <row r="5" spans="2:13">
       <c r="G5" s="26">
         <v>4</v>
       </c>
@@ -12548,7 +12558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="7:13">
+    <row r="6" spans="2:13">
       <c r="G6" s="28">
         <v>5</v>
       </c>
@@ -12571,7 +12581,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="7:13">
+    <row r="7" spans="2:13">
       <c r="G7" s="18">
         <v>6</v>
       </c>
@@ -12591,7 +12601,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="8" spans="7:13">
+    <row r="8" spans="2:13">
       <c r="G8" s="26">
         <v>7</v>
       </c>
@@ -12611,7 +12621,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="9" spans="7:13">
+    <row r="9" spans="2:13">
       <c r="G9" s="28">
         <v>8</v>
       </c>
@@ -12631,7 +12641,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="10" spans="7:13">
+    <row r="10" spans="2:13">
       <c r="G10" s="18">
         <v>9</v>
       </c>
@@ -12654,7 +12664,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="7:13">
+    <row r="11" spans="2:13">
       <c r="G11" s="26">
         <v>10</v>
       </c>
@@ -12674,7 +12684,9 @@
         <v>538</v>
       </c>
     </row>
-    <row r="12" spans="7:13">
+    <row r="12" spans="2:13">
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
       <c r="G12" s="28">
         <v>11</v>
       </c>
@@ -12694,7 +12706,11 @@
         <v>543</v>
       </c>
     </row>
-    <row r="13" spans="7:13">
+    <row r="13" spans="2:13">
+      <c r="B13" s="31" t="s">
+        <v>586</v>
+      </c>
+      <c r="C13" s="17"/>
       <c r="G13" s="28">
         <v>12</v>
       </c>
@@ -12714,7 +12730,11 @@
         <v>544</v>
       </c>
     </row>
-    <row r="14" spans="7:13">
+    <row r="14" spans="2:13">
+      <c r="B14" s="31" t="s">
+        <v>587</v>
+      </c>
+      <c r="C14" s="17"/>
       <c r="G14" s="18">
         <v>13</v>
       </c>
@@ -12737,7 +12757,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="7:13">
+    <row r="15" spans="2:13">
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
       <c r="G15" s="26">
         <v>14</v>
       </c>
@@ -12757,7 +12779,13 @@
         <v>546</v>
       </c>
     </row>
-    <row r="16" spans="7:13">
+    <row r="16" spans="2:13">
+      <c r="B16" s="27" t="s">
+        <v>213</v>
+      </c>
+      <c r="C16" s="27" t="s">
+        <v>217</v>
+      </c>
       <c r="G16" s="26">
         <v>15</v>
       </c>
@@ -12777,7 +12805,13 @@
         <v>547</v>
       </c>
     </row>
-    <row r="17" spans="7:12">
+    <row r="17" spans="2:12">
+      <c r="B17" s="29" t="s">
+        <v>293</v>
+      </c>
+      <c r="C17" s="29" t="s">
+        <v>299</v>
+      </c>
       <c r="G17" s="28">
         <v>16</v>
       </c>
@@ -12797,7 +12831,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="18" spans="7:12">
+    <row r="18" spans="2:12">
       <c r="G18" s="18">
         <v>17</v>
       </c>
@@ -12817,7 +12851,13 @@
         <v>548</v>
       </c>
     </row>
-    <row r="19" spans="7:12">
+    <row r="19" spans="2:12">
+      <c r="B19" s="29" t="s">
+        <v>296</v>
+      </c>
+      <c r="C19" s="28" t="s">
+        <v>297</v>
+      </c>
       <c r="G19" s="26">
         <v>18</v>
       </c>
@@ -12837,7 +12877,13 @@
         <v>549</v>
       </c>
     </row>
-    <row r="20" spans="7:12">
+    <row r="20" spans="2:12">
+      <c r="B20" s="29" t="s">
+        <v>302</v>
+      </c>
+      <c r="C20" s="28" t="s">
+        <v>303</v>
+      </c>
       <c r="G20" s="28">
         <v>19</v>
       </c>
@@ -12857,7 +12903,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="21" spans="7:12">
+    <row r="21" spans="2:12">
       <c r="G21" s="28">
         <v>20</v>
       </c>
@@ -12877,7 +12923,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="22" spans="7:12">
+    <row r="22" spans="2:12">
       <c r="G22" s="24">
         <v>21</v>
       </c>
@@ -12897,7 +12943,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="23" spans="7:12">
+    <row r="23" spans="2:12">
       <c r="G23" s="26">
         <v>22</v>
       </c>
@@ -12917,7 +12963,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="24" spans="7:12">
+    <row r="24" spans="2:12">
       <c r="G24" s="28">
         <v>23</v>
       </c>
@@ -12937,7 +12983,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="25" spans="7:12">
+    <row r="25" spans="2:12">
       <c r="G25" s="18">
         <v>24</v>
       </c>
@@ -12957,7 +13003,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="26" spans="7:12">
+    <row r="26" spans="2:12">
       <c r="G26" s="26">
         <v>25</v>
       </c>
@@ -12977,7 +13023,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="27" spans="7:12">
+    <row r="27" spans="2:12">
       <c r="G27" s="28">
         <v>26</v>
       </c>
@@ -12997,7 +13043,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="28" spans="7:12">
+    <row r="28" spans="2:12">
       <c r="G28" s="20">
         <v>27</v>
       </c>
@@ -13017,7 +13063,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="29" spans="7:12">
+    <row r="29" spans="2:12">
       <c r="G29" s="20">
         <v>28</v>
       </c>
@@ -13037,7 +13083,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="30" spans="7:12">
+    <row r="30" spans="2:12">
       <c r="G30" s="20">
         <v>29</v>
       </c>
@@ -13057,7 +13103,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="31" spans="7:12">
+    <row r="31" spans="2:12">
       <c r="G31" s="26">
         <v>30</v>
       </c>
@@ -13077,7 +13123,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="32" spans="7:12">
+    <row r="32" spans="2:12">
       <c r="G32" s="28">
         <v>31</v>
       </c>
@@ -13417,7 +13463,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="49" spans="7:12">
+    <row r="49" spans="7:13">
       <c r="G49" s="28">
         <v>48</v>
       </c>
@@ -13437,7 +13483,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="50" spans="7:12">
+    <row r="50" spans="7:13">
       <c r="G50" s="26">
         <v>49</v>
       </c>
@@ -13456,8 +13502,11 @@
       <c r="L50" s="26" t="s">
         <v>549</v>
       </c>
-    </row>
-    <row r="51" spans="7:12">
+      <c r="M50" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="7:13">
       <c r="G51" s="28">
         <v>50</v>
       </c>
@@ -13477,7 +13526,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="52" spans="7:12">
+    <row r="52" spans="7:13">
       <c r="G52" s="20">
         <v>51</v>
       </c>
@@ -13497,7 +13546,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="53" spans="7:12">
+    <row r="53" spans="7:13">
       <c r="G53" s="22">
         <v>52</v>
       </c>
@@ -13517,7 +13566,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="54" spans="7:12">
+    <row r="54" spans="7:13">
       <c r="G54" s="22">
         <v>53</v>
       </c>
@@ -13537,7 +13586,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="55" spans="7:12">
+    <row r="55" spans="7:13">
       <c r="G55" s="26">
         <v>54</v>
       </c>
@@ -13557,7 +13606,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="56" spans="7:12">
+    <row r="56" spans="7:13">
       <c r="G56" s="28">
         <v>55</v>
       </c>
@@ -13577,7 +13626,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="57" spans="7:12">
+    <row r="57" spans="7:13">
       <c r="G57" s="22">
         <v>56</v>
       </c>
@@ -13597,7 +13646,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="58" spans="7:12">
+    <row r="58" spans="7:13">
       <c r="G58" s="22">
         <v>57</v>
       </c>
@@ -13617,7 +13666,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="59" spans="7:12">
+    <row r="59" spans="7:13">
       <c r="G59" s="22">
         <v>58</v>
       </c>
@@ -13637,7 +13686,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="60" spans="7:12">
+    <row r="60" spans="7:13">
       <c r="G60" s="22">
         <v>59</v>
       </c>
@@ -13657,7 +13706,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="61" spans="7:12">
+    <row r="61" spans="7:13">
       <c r="G61" s="22">
         <v>60</v>
       </c>
@@ -13677,7 +13726,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="62" spans="7:12">
+    <row r="62" spans="7:13">
       <c r="G62" s="26">
         <v>61</v>
       </c>
@@ -13697,7 +13746,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="63" spans="7:12">
+    <row r="63" spans="7:13">
       <c r="G63" s="28">
         <v>62</v>
       </c>
@@ -13717,7 +13766,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="64" spans="7:12">
+    <row r="64" spans="7:13">
       <c r="G64" s="24">
         <v>63</v>
       </c>
@@ -13942,6 +13991,7 @@
     <sortCondition ref="G2:G84"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
